--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3051,9 +3051,14 @@
       <c r="E76" s="4" t="n">
         <v>46278.04375</v>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1841631163883906</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3084,9 +3084,14 @@
       <c r="E77" s="4" t="n">
         <v>46278.73125</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1303286461767654</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3117,9 +3117,14 @@
       <c r="E78" s="4" t="n">
         <v>46278.98125</v>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>3207315969462188</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3150,9 +3150,14 @@
       <c r="E79" s="4" t="n">
         <v>46279.04375</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1350339548158186</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3183,9 +3183,14 @@
       <c r="E80" s="4" t="n">
         <v>46279.73125</v>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1760103025045539</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3216,9 +3216,14 @@
       <c r="E81" s="4" t="n">
         <v>46279.98125</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>4543528849242639</t>
         </is>
       </c>
     </row>
@@ -3244,9 +3249,14 @@
       <c r="E82" s="4" t="n">
         <v>46280.04375</v>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1802696837530956</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3282,9 +3282,14 @@
       <c r="E83" s="4" t="n">
         <v>46280.73125</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1961014554574412</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3315,9 +3315,14 @@
       <c r="E84" s="4" t="n">
         <v>46280.98125</v>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1789440848743010</t>
         </is>
       </c>
     </row>
@@ -3343,9 +3348,14 @@
       <c r="E85" s="4" t="n">
         <v>46281.04375</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2526740011086130</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3381,9 +3381,14 @@
       <c r="E86" s="4" t="n">
         <v>46281.73125</v>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1406007067551186</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3414,9 +3414,14 @@
       <c r="E87" s="4" t="n">
         <v>46281.98125</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>4434311726842159</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3447,9 +3447,14 @@
       <c r="E88" s="4" t="n">
         <v>46282.04375</v>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1408576428039683</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3480,9 +3480,14 @@
       <c r="E89" s="4" t="n">
         <v>46282.73125</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2177904806439572</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3513,9 +3513,14 @@
       <c r="E90" s="4" t="n">
         <v>46282.98125</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>940733998556834</t>
         </is>
       </c>
     </row>
@@ -3541,9 +3546,14 @@
       <c r="E91" s="4" t="n">
         <v>46283.04375</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1422132959851068</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3579,9 +3579,14 @@
       <c r="E92" s="4" t="n">
         <v>46283.73125</v>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1085843104055115</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3612,9 +3612,14 @@
       <c r="E93" s="4" t="n">
         <v>46283.98125</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1420105256760313</t>
         </is>
       </c>
     </row>
@@ -3640,9 +3645,14 @@
       <c r="E94" s="4" t="n">
         <v>46284.04375</v>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2229716467875156</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3678,9 +3678,14 @@
       <c r="E95" s="4" t="n">
         <v>46284.73125</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2422285658174992</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3711,9 +3711,14 @@
       <c r="E96" s="4" t="n">
         <v>46284.98125</v>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2547253682452215</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3744,9 +3744,14 @@
       <c r="E97" s="4" t="n">
         <v>46285.04375</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1414657670692145</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3777,9 +3777,14 @@
       <c r="E98" s="4" t="n">
         <v>46285.73125</v>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1327199915998016</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3810,9 +3810,14 @@
       <c r="E99" s="4" t="n">
         <v>46285.98125</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1618448419947667</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3843,9 +3843,14 @@
       <c r="E100" s="4" t="n">
         <v>46286.04375</v>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1083784844242782</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3876,9 +3876,14 @@
       <c r="E101" s="4" t="n">
         <v>46286.73125</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>3834753709998370</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3909,9 +3909,14 @@
       <c r="E102" s="4" t="n">
         <v>46286.98125</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F102" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1645974206892549</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3942,9 +3942,14 @@
       <c r="E103" s="4" t="n">
         <v>46287.04375</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1760097705134304</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3975,9 +3975,14 @@
       <c r="E104" s="4" t="n">
         <v>46287.73125</v>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2342819576522416</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4008,9 +4008,14 @@
       <c r="E105" s="4" t="n">
         <v>46287.98125</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1560036841991447</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4041,9 +4041,14 @@
       <c r="E106" s="4" t="n">
         <v>46288.04375</v>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1049701604364140</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4074,9 +4074,14 @@
       <c r="E107" s="4" t="n">
         <v>46288.73125</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1918156469188312</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4107,9 +4107,14 @@
       <c r="E108" s="4" t="n">
         <v>46288.98125</v>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>28505665989075655</t>
         </is>
       </c>
     </row>
@@ -4135,9 +4140,14 @@
       <c r="E109" s="4" t="n">
         <v>46289.04375</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1632461654907019</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4173,9 +4173,14 @@
       <c r="E110" s="4" t="n">
         <v>46289.73125</v>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1728075638277036</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4206,9 +4206,14 @@
       <c r="E111" s="4" t="n">
         <v>46289.98125</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2350349422372810</t>
         </is>
       </c>
     </row>
@@ -4234,9 +4239,14 @@
       <c r="E112" s="4" t="n">
         <v>46290.04375</v>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1400642945580823</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4272,9 +4272,14 @@
       <c r="E113" s="4" t="n">
         <v>46290.73125</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1611615837097168</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4305,9 +4305,14 @@
       <c r="E114" s="4" t="n">
         <v>46290.98125</v>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1047268144982151</t>
         </is>
       </c>
     </row>
@@ -4333,9 +4338,14 @@
       <c r="E115" s="4" t="n">
         <v>46291.04375</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1940278423597582</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4371,9 +4371,14 @@
       <c r="E116" s="4" t="n">
         <v>46291.73125</v>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1110363334782733</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4401,9 +4401,14 @@
       <c r="E117" s="4" t="n">
         <v>46291.98125</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>28448111991483968</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4431,9 +4431,14 @@
       <c r="E118" s="4" t="n">
         <v>46292.04375</v>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1324145099645874</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4461,9 +4461,14 @@
       <c r="E119" s="4" t="n">
         <v>46292.73125</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1502100871665616</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4494,9 +4494,14 @@
       <c r="E120" s="4" t="n">
         <v>46292.98125</v>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2189732641573516</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4527,9 +4527,14 @@
       <c r="E121" s="4" t="n">
         <v>46293.04375</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1410974454344680</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4560,9 +4560,14 @@
       <c r="E122" s="4" t="n">
         <v>46293.73125</v>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1439418271627010</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4593,9 +4593,14 @@
       <c r="E123" s="4" t="n">
         <v>46293.98125</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1709693020132872</t>
         </is>
       </c>
     </row>
@@ -4621,9 +4626,14 @@
       <c r="E124" s="4" t="n">
         <v>46294.04375</v>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1620568359714916</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4659,9 +4659,14 @@
       <c r="E125" s="4" t="n">
         <v>46294.73125</v>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2060476814632857</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4692,9 +4692,14 @@
       <c r="E126" s="4" t="n">
         <v>46294.98125</v>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1077567358211953</t>
         </is>
       </c>
     </row>
@@ -4720,9 +4725,14 @@
       <c r="E127" s="4" t="n">
         <v>46295.04375</v>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1781219506430992</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4758,9 +4758,14 @@
       <c r="E128" s="4" t="n">
         <v>46295.73125</v>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2328109708003382</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4791,9 +4791,14 @@
       <c r="E129" s="4" t="n">
         <v>46295.98125</v>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1799396247767191</t>
         </is>
       </c>
     </row>
@@ -4819,9 +4824,14 @@
       <c r="E130" s="4" t="n">
         <v>46296.04375</v>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1479603670725417</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4857,9 +4857,14 @@
       <c r="E131" s="4" t="n">
         <v>46296.73125</v>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1083841504512474</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4890,9 +4890,14 @@
       <c r="E132" s="4" t="n">
         <v>46296.98125</v>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1095161286805317</t>
         </is>
       </c>
     </row>
@@ -4918,9 +4923,14 @@
       <c r="E133" s="4" t="n">
         <v>46297.04375</v>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1972984270061342</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4956,9 +4956,14 @@
       <c r="E134" s="4" t="n">
         <v>46297.73125</v>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1628770485500538</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4989,9 +4989,14 @@
       <c r="E135" s="4" t="n">
         <v>46297.98125</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1617700566755789</t>
         </is>
       </c>
     </row>
